--- a/src/features/quotations/utils/fixtures/row-error.xlsx
+++ b/src/features/quotations/utils/fixtures/row-error.xlsx
@@ -415,6 +415,10 @@
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -459,12 +463,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>markup_override</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>tax_class</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>markup_override</t>
         </is>
       </c>
     </row>
